--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121136088</v>
+        <v>121136708</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>91973</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598465</v>
+        <v>598475</v>
       </c>
       <c r="R2" t="n">
-        <v>6420653</v>
+        <v>6420787</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121136256</v>
+        <v>121136088</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598497</v>
+        <v>598465</v>
       </c>
       <c r="R3" t="n">
-        <v>6420665</v>
+        <v>6420653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121136243</v>
+        <v>121136256</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598487</v>
+        <v>598497</v>
       </c>
       <c r="R4" t="n">
-        <v>6420649</v>
+        <v>6420665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121136638</v>
+        <v>121136217</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598505</v>
+        <v>598477</v>
       </c>
       <c r="R5" t="n">
-        <v>6420652</v>
+        <v>6420659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121136708</v>
+        <v>121135992</v>
       </c>
       <c r="B6" t="n">
-        <v>91963</v>
+        <v>91102</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,26 +1138,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1170,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598475</v>
+        <v>598432</v>
       </c>
       <c r="R6" t="n">
-        <v>6420787</v>
+        <v>6420560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121135992</v>
+        <v>121136685</v>
       </c>
       <c r="B7" t="n">
-        <v>91092</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,38 +1248,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,13 +1288,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598432</v>
+        <v>598531</v>
       </c>
       <c r="R7" t="n">
-        <v>6420560</v>
+        <v>6420696</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1328,7 +1332,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>121136718</v>
       </c>
       <c r="B8" t="n">
-        <v>90707</v>
+        <v>90717</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1464,7 +1467,7 @@
         <v>121136651</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1572,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121136685</v>
+        <v>121136096</v>
       </c>
       <c r="B10" t="n">
-        <v>57501</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,39 +1587,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1624,13 +1623,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598531</v>
+        <v>598463</v>
       </c>
       <c r="R10" t="n">
-        <v>6420696</v>
+        <v>6420649</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,6 +1667,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1686,10 +1686,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121136699</v>
+        <v>121136660</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598531</v>
+        <v>598556</v>
       </c>
       <c r="R11" t="n">
-        <v>6420690</v>
+        <v>6420694</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121136660</v>
+        <v>121136229</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598556</v>
+        <v>598490</v>
       </c>
       <c r="R12" t="n">
-        <v>6420694</v>
+        <v>6420655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121135855</v>
+        <v>121136638</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598430</v>
+        <v>598505</v>
       </c>
       <c r="R13" t="n">
-        <v>6420563</v>
+        <v>6420652</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121136096</v>
+        <v>121135855</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598463</v>
+        <v>598430</v>
       </c>
       <c r="R14" t="n">
-        <v>6420649</v>
+        <v>6420563</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121136229</v>
+        <v>121136699</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598490</v>
+        <v>598531</v>
       </c>
       <c r="R15" t="n">
-        <v>6420655</v>
+        <v>6420690</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121136217</v>
+        <v>121136243</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598477</v>
+        <v>598487</v>
       </c>
       <c r="R16" t="n">
-        <v>6420659</v>
+        <v>6420649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121135992</v>
+        <v>121136685</v>
       </c>
       <c r="B6" t="n">
-        <v>91102</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,38 +1134,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1173,13 +1174,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598432</v>
+        <v>598531</v>
       </c>
       <c r="R6" t="n">
-        <v>6420560</v>
+        <v>6420696</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1217,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121136685</v>
+        <v>121135992</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>91102</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,39 +1248,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1288,13 +1287,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598531</v>
+        <v>598432</v>
       </c>
       <c r="R7" t="n">
-        <v>6420696</v>
+        <v>6420560</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1332,6 +1331,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121136708</v>
+        <v>121136256</v>
       </c>
       <c r="B2" t="n">
-        <v>91973</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598475</v>
+        <v>598497</v>
       </c>
       <c r="R2" t="n">
-        <v>6420787</v>
+        <v>6420665</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121136088</v>
+        <v>121136699</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598465</v>
+        <v>598531</v>
       </c>
       <c r="R3" t="n">
-        <v>6420653</v>
+        <v>6420690</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121136256</v>
+        <v>121136217</v>
       </c>
       <c r="B4" t="n">
         <v>98081</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598497</v>
+        <v>598477</v>
       </c>
       <c r="R4" t="n">
-        <v>6420665</v>
+        <v>6420659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121136217</v>
+        <v>121136685</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,35 +1020,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1059,13 +1060,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598477</v>
+        <v>598531</v>
       </c>
       <c r="R5" t="n">
-        <v>6420659</v>
+        <v>6420696</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,7 +1104,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121136685</v>
+        <v>121136660</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,39 +1134,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598531</v>
+        <v>598556</v>
       </c>
       <c r="R6" t="n">
-        <v>6420696</v>
+        <v>6420694</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1214,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121135992</v>
+        <v>121136096</v>
       </c>
       <c r="B7" t="n">
-        <v>91102</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,38 +1245,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1287,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598432</v>
+        <v>598463</v>
       </c>
       <c r="R7" t="n">
-        <v>6420560</v>
+        <v>6420649</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1464,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121136651</v>
+        <v>121135992</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>91102</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,35 +1470,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1512,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598528</v>
+        <v>598432</v>
       </c>
       <c r="R9" t="n">
-        <v>6420670</v>
+        <v>6420560</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1575,7 +1572,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121136096</v>
+        <v>121136088</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1623,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598463</v>
+        <v>598465</v>
       </c>
       <c r="R10" t="n">
-        <v>6420649</v>
+        <v>6420653</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121136660</v>
+        <v>121136638</v>
       </c>
       <c r="B11" t="n">
         <v>98081</v>
@@ -1734,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598556</v>
+        <v>598505</v>
       </c>
       <c r="R11" t="n">
-        <v>6420694</v>
+        <v>6420652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1794,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121136229</v>
+        <v>121136651</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1845,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598490</v>
+        <v>598528</v>
       </c>
       <c r="R12" t="n">
-        <v>6420655</v>
+        <v>6420670</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121136638</v>
+        <v>121136229</v>
       </c>
       <c r="B13" t="n">
         <v>98081</v>
@@ -1956,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598505</v>
+        <v>598490</v>
       </c>
       <c r="R13" t="n">
-        <v>6420652</v>
+        <v>6420655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121135855</v>
+        <v>121136708</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>91973</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,35 +2028,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598430</v>
+        <v>598475</v>
       </c>
       <c r="R14" t="n">
-        <v>6420563</v>
+        <v>6420787</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121136699</v>
+        <v>121136243</v>
       </c>
       <c r="B15" t="n">
         <v>98081</v>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598531</v>
+        <v>598487</v>
       </c>
       <c r="R15" t="n">
-        <v>6420690</v>
+        <v>6420649</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121136243</v>
+        <v>121135855</v>
       </c>
       <c r="B16" t="n">
         <v>98081</v>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598487</v>
+        <v>598430</v>
       </c>
       <c r="R16" t="n">
-        <v>6420649</v>
+        <v>6420563</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121136256</v>
+        <v>121136096</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598497</v>
+        <v>598463</v>
       </c>
       <c r="R2" t="n">
-        <v>6420665</v>
+        <v>6420649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121136699</v>
+        <v>121135855</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598531</v>
+        <v>598430</v>
       </c>
       <c r="R3" t="n">
-        <v>6420690</v>
+        <v>6420563</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121136217</v>
+        <v>121136638</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598477</v>
+        <v>598505</v>
       </c>
       <c r="R4" t="n">
-        <v>6420659</v>
+        <v>6420652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121136685</v>
+        <v>121136088</v>
       </c>
       <c r="B5" t="n">
-        <v>57504</v>
+        <v>98094</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,39 +1020,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1060,13 +1056,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598531</v>
+        <v>598465</v>
       </c>
       <c r="R5" t="n">
-        <v>6420696</v>
+        <v>6420653</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1104,6 +1100,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121136660</v>
+        <v>121136685</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1170,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598556</v>
+        <v>598531</v>
       </c>
       <c r="R6" t="n">
-        <v>6420694</v>
+        <v>6420696</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1214,7 +1215,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1233,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121136096</v>
+        <v>121136660</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598463</v>
+        <v>598556</v>
       </c>
       <c r="R7" t="n">
-        <v>6420649</v>
+        <v>6420694</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121136718</v>
+        <v>121136217</v>
       </c>
       <c r="B8" t="n">
-        <v>90717</v>
+        <v>98094</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,38 +1356,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1395,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598454</v>
+        <v>598477</v>
       </c>
       <c r="R8" t="n">
-        <v>6420711</v>
+        <v>6420659</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1455,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121135992</v>
+        <v>121136651</v>
       </c>
       <c r="B9" t="n">
-        <v>91102</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,38 +1467,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1509,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598432</v>
+        <v>598528</v>
       </c>
       <c r="R9" t="n">
-        <v>6420560</v>
+        <v>6420670</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,10 +1566,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121136088</v>
+        <v>121136718</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>90729</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,35 +1578,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598465</v>
+        <v>598454</v>
       </c>
       <c r="R10" t="n">
-        <v>6420653</v>
+        <v>6420711</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121136638</v>
+        <v>121136699</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598505</v>
+        <v>598531</v>
       </c>
       <c r="R11" t="n">
-        <v>6420652</v>
+        <v>6420690</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1791,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121136651</v>
+        <v>121136229</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598528</v>
+        <v>598490</v>
       </c>
       <c r="R12" t="n">
-        <v>6420670</v>
+        <v>6420655</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,10 +1902,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121136229</v>
+        <v>121136256</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598490</v>
+        <v>598497</v>
       </c>
       <c r="R13" t="n">
-        <v>6420655</v>
+        <v>6420665</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2016,7 @@
         <v>121136708</v>
       </c>
       <c r="B14" t="n">
-        <v>91973</v>
+        <v>91985</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2133,7 +2130,7 @@
         <v>121136243</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2241,10 +2238,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121135855</v>
+        <v>121135992</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>91114</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2253,35 +2250,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598430</v>
+        <v>598432</v>
       </c>
       <c r="R16" t="n">
-        <v>6420563</v>
+        <v>6420560</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121136096</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121135855</v>
+        <v>121136718</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>90730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,35 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598430</v>
+        <v>598454</v>
       </c>
       <c r="R3" t="n">
-        <v>6420563</v>
+        <v>6420711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121136638</v>
+        <v>121136088</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598505</v>
+        <v>598465</v>
       </c>
       <c r="R4" t="n">
-        <v>6420652</v>
+        <v>6420653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121136088</v>
+        <v>121136217</v>
       </c>
       <c r="B5" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598465</v>
+        <v>598477</v>
       </c>
       <c r="R5" t="n">
-        <v>6420653</v>
+        <v>6420659</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1233,10 +1236,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121136660</v>
+        <v>121136699</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598556</v>
+        <v>598531</v>
       </c>
       <c r="R7" t="n">
-        <v>6420694</v>
+        <v>6420690</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121136217</v>
+        <v>121135992</v>
       </c>
       <c r="B8" t="n">
-        <v>98094</v>
+        <v>91115</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,35 +1359,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1392,10 +1398,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598477</v>
+        <v>598432</v>
       </c>
       <c r="R8" t="n">
-        <v>6420659</v>
+        <v>6420560</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1455,10 +1461,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121136651</v>
+        <v>121136243</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598528</v>
+        <v>598487</v>
       </c>
       <c r="R9" t="n">
-        <v>6420670</v>
+        <v>6420649</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1566,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121136718</v>
+        <v>121136651</v>
       </c>
       <c r="B10" t="n">
-        <v>90729</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1578,38 +1584,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1617,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598454</v>
+        <v>598528</v>
       </c>
       <c r="R10" t="n">
-        <v>6420711</v>
+        <v>6420670</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121136699</v>
+        <v>121136638</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1728,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598531</v>
+        <v>598505</v>
       </c>
       <c r="R11" t="n">
-        <v>6420690</v>
+        <v>6420652</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1791,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121136229</v>
+        <v>121135855</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1839,10 +1842,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598490</v>
+        <v>598430</v>
       </c>
       <c r="R12" t="n">
-        <v>6420655</v>
+        <v>6420563</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1905,7 +1908,7 @@
         <v>121136256</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,10 +2016,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121136708</v>
+        <v>121136229</v>
       </c>
       <c r="B14" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2025,38 +2028,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598475</v>
+        <v>598490</v>
       </c>
       <c r="R14" t="n">
-        <v>6420787</v>
+        <v>6420655</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121136243</v>
+        <v>121136708</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2139,35 +2139,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2175,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598487</v>
+        <v>598475</v>
       </c>
       <c r="R15" t="n">
-        <v>6420649</v>
+        <v>6420787</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121135992</v>
+        <v>121136660</v>
       </c>
       <c r="B16" t="n">
-        <v>91114</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2250,38 +2253,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598432</v>
+        <v>598556</v>
       </c>
       <c r="R16" t="n">
-        <v>6420560</v>
+        <v>6420694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121136096</v>
+        <v>121135992</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>91118</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598463</v>
+        <v>598432</v>
       </c>
       <c r="R2" t="n">
-        <v>6420649</v>
+        <v>6420560</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121136718</v>
+        <v>121136651</v>
       </c>
       <c r="B3" t="n">
-        <v>90730</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598454</v>
+        <v>598528</v>
       </c>
       <c r="R3" t="n">
-        <v>6420711</v>
+        <v>6420670</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121136088</v>
+        <v>121136243</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598465</v>
+        <v>598487</v>
       </c>
       <c r="R4" t="n">
-        <v>6420653</v>
+        <v>6420649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121136217</v>
+        <v>121136256</v>
       </c>
       <c r="B5" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598477</v>
+        <v>598497</v>
       </c>
       <c r="R5" t="n">
-        <v>6420659</v>
+        <v>6420665</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1122,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121136685</v>
+        <v>121136718</v>
       </c>
       <c r="B6" t="n">
-        <v>57504</v>
+        <v>90733</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1138,21 +1138,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1160,13 +1160,12 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1174,13 +1173,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598531</v>
+        <v>598454</v>
       </c>
       <c r="R6" t="n">
-        <v>6420696</v>
+        <v>6420711</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1218,6 +1217,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>121136699</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121135992</v>
+        <v>121136660</v>
       </c>
       <c r="B8" t="n">
-        <v>91115</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,38 +1359,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598432</v>
+        <v>598556</v>
       </c>
       <c r="R8" t="n">
-        <v>6420560</v>
+        <v>6420694</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121136243</v>
+        <v>121136096</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,7 +1506,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598487</v>
+        <v>598463</v>
       </c>
       <c r="R9" t="n">
         <v>6420649</v>
@@ -1572,10 +1569,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121136651</v>
+        <v>121136708</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1584,35 +1581,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598528</v>
+        <v>598475</v>
       </c>
       <c r="R10" t="n">
-        <v>6420670</v>
+        <v>6420787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121136638</v>
+        <v>121136217</v>
       </c>
       <c r="B11" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598505</v>
+        <v>598477</v>
       </c>
       <c r="R11" t="n">
-        <v>6420652</v>
+        <v>6420659</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121135855</v>
+        <v>121136685</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>57507</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,35 +1806,39 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1842,13 +1846,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598430</v>
+        <v>598531</v>
       </c>
       <c r="R12" t="n">
-        <v>6420563</v>
+        <v>6420696</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1886,7 +1890,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1905,10 +1908,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121136256</v>
+        <v>121135855</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1953,10 +1956,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598497</v>
+        <v>598430</v>
       </c>
       <c r="R13" t="n">
-        <v>6420665</v>
+        <v>6420563</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121136229</v>
+        <v>121136088</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2064,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598490</v>
+        <v>598465</v>
       </c>
       <c r="R14" t="n">
-        <v>6420655</v>
+        <v>6420653</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2127,10 +2130,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121136708</v>
+        <v>121136638</v>
       </c>
       <c r="B15" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2139,38 +2142,35 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598475</v>
+        <v>598505</v>
       </c>
       <c r="R15" t="n">
-        <v>6420787</v>
+        <v>6420652</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121136660</v>
+        <v>121136229</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598556</v>
+        <v>598490</v>
       </c>
       <c r="R16" t="n">
-        <v>6420694</v>
+        <v>6420655</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 48724-2024 artfynd.xlsx
+++ b/artfynd/A 48724-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121135992</v>
+        <v>121136243</v>
       </c>
       <c r="B2" t="n">
-        <v>91118</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -726,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>598432</v>
+        <v>598487</v>
       </c>
       <c r="R2" t="n">
-        <v>6420560</v>
+        <v>6420649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -789,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121136651</v>
+        <v>121136096</v>
       </c>
       <c r="B3" t="n">
         <v>98098</v>
@@ -837,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598528</v>
+        <v>598463</v>
       </c>
       <c r="R3" t="n">
-        <v>6420670</v>
+        <v>6420649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -900,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121136243</v>
+        <v>121136217</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -948,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598487</v>
+        <v>598477</v>
       </c>
       <c r="R4" t="n">
-        <v>6420649</v>
+        <v>6420659</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121136256</v>
+        <v>121136699</v>
       </c>
       <c r="B5" t="n">
         <v>98098</v>
@@ -1059,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598497</v>
+        <v>598531</v>
       </c>
       <c r="R5" t="n">
-        <v>6420665</v>
+        <v>6420690</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1122,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121136718</v>
+        <v>121135992</v>
       </c>
       <c r="B6" t="n">
-        <v>90733</v>
+        <v>91118</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1134,30 +1131,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1173,10 +1170,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598454</v>
+        <v>598432</v>
       </c>
       <c r="R6" t="n">
-        <v>6420711</v>
+        <v>6420560</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121136699</v>
+        <v>121136708</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,35 +1245,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598531</v>
+        <v>598475</v>
       </c>
       <c r="R7" t="n">
-        <v>6420690</v>
+        <v>6420787</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121136660</v>
+        <v>121136638</v>
       </c>
       <c r="B8" t="n">
         <v>98098</v>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598556</v>
+        <v>598505</v>
       </c>
       <c r="R8" t="n">
-        <v>6420694</v>
+        <v>6420652</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,10 +1458,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121136096</v>
+        <v>121136685</v>
       </c>
       <c r="B9" t="n">
-        <v>98098</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1470,35 +1470,39 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1506,13 +1510,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598463</v>
+        <v>598531</v>
       </c>
       <c r="R9" t="n">
-        <v>6420649</v>
+        <v>6420696</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1550,7 +1554,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1569,10 +1572,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121136708</v>
+        <v>121136256</v>
       </c>
       <c r="B10" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1581,38 +1584,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1620,10 +1620,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598475</v>
+        <v>598497</v>
       </c>
       <c r="R10" t="n">
-        <v>6420787</v>
+        <v>6420665</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121136217</v>
+        <v>121136088</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1731,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598477</v>
+        <v>598465</v>
       </c>
       <c r="R11" t="n">
-        <v>6420659</v>
+        <v>6420653</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,10 +1794,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121136685</v>
+        <v>121135855</v>
       </c>
       <c r="B12" t="n">
-        <v>57507</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1806,39 +1806,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1846,13 +1842,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598531</v>
+        <v>598430</v>
       </c>
       <c r="R12" t="n">
-        <v>6420696</v>
+        <v>6420563</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1890,6 +1886,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1908,7 +1905,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121135855</v>
+        <v>121136229</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -1956,10 +1953,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598430</v>
+        <v>598490</v>
       </c>
       <c r="R13" t="n">
-        <v>6420563</v>
+        <v>6420655</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121136088</v>
+        <v>121136651</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -2067,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598465</v>
+        <v>598528</v>
       </c>
       <c r="R14" t="n">
-        <v>6420653</v>
+        <v>6420670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,10 +2127,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121136638</v>
+        <v>121136718</v>
       </c>
       <c r="B15" t="n">
-        <v>98098</v>
+        <v>90733</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2142,35 +2139,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598505</v>
+        <v>598454</v>
       </c>
       <c r="R15" t="n">
-        <v>6420652</v>
+        <v>6420711</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121136229</v>
+        <v>121136660</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598490</v>
+        <v>598556</v>
       </c>
       <c r="R16" t="n">
-        <v>6420655</v>
+        <v>6420694</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
